--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604C06C6-2D5C-4FE3-ACAA-6DF8CDF525A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8E3832-BEDA-4283-8A38-255DF2A83B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="821">
   <si>
     <t>Prénom</t>
   </si>
@@ -46,7 +46,7 @@
     <t>Date de création</t>
   </si>
   <si>
-    <t xml:space="preserve">Ville de création </t>
+    <t>Lieu de conservation</t>
   </si>
   <si>
     <t>Lieu précis de conservation</t>
@@ -154,6 +154,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Still_Life_with_Checked_Tablecloth_MET_DP332907_ms.jpg/1280px-Still_Life_with_Checked_Tablecloth_MET_DP332907_ms.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>116,5 cm</t>
+  </si>
+  <si>
+    <t>89,2 cm</t>
+  </si>
+  <si>
     <t>1922</t>
   </si>
   <si>
@@ -166,6 +172,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/Gris%2C_Nature_morte_%28_Mus%C3%A9e_d%27art_moderne_et_contemporain_de_Strasbourg_%29.JPG/1280px-Gris%2C_Nature_morte_%28_Mus%C3%A9e_d%27art_moderne_et_contemporain_de_Strasbourg_%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>25 cm</t>
+  </si>
+  <si>
+    <t>32,8 cm</t>
+  </si>
+  <si>
     <t>Hilma</t>
   </si>
   <si>
@@ -247,6 +259,12 @@
     <t>Gouache et crayon sur papier</t>
   </si>
   <si>
+    <t>34 cm</t>
+  </si>
+  <si>
+    <t>21 cm</t>
+  </si>
+  <si>
     <t>russe</t>
   </si>
   <si>
@@ -391,6 +409,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Pierre_Bonnard%2C_1908_-_Nu_%C3%A0_contre-jour.jpg/1280px-Pierre_Bonnard%2C_1908_-_Nu_%C3%A0_contre-jour.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>124,5 cm</t>
+  </si>
+  <si>
+    <t>109 cm</t>
+  </si>
+  <si>
     <t>française</t>
   </si>
   <si>
@@ -439,6 +463,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/ca/Pierre_Bonnard_Flowering_Almond_Tree.jpg/1280px-Pierre_Bonnard_Flowering_Almond_Tree.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>54,5 cm</t>
+  </si>
+  <si>
+    <t>37,5 cm</t>
+  </si>
+  <si>
     <t>Lovis</t>
   </si>
   <si>
@@ -463,6 +493,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Lovis_Corinth_-_Julius_Meier-Graefe.jpg/1280px-Lovis_Corinth_-_Julius_Meier-Graefe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>90,4 cm</t>
+  </si>
+  <si>
+    <t>70,4 cm</t>
+  </si>
+  <si>
     <t>Berlin</t>
   </si>
   <si>
@@ -547,6 +583,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/Robert_delaunay%2C_tour_eiffel%2C_1926.jpg/1280px-Robert_delaunay%2C_tour_eiffel%2C_1926.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>170 cm</t>
+  </si>
+  <si>
+    <t>104 cm</t>
+  </si>
+  <si>
     <t>André</t>
   </si>
   <si>
@@ -664,6 +706,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/04/Raoul_Dufy_-_L%27Estaque_-_1992.123_-_Rhode_Island_School_of_Design_Museum.jpg/1280px-Raoul_Dufy_-_L%27Estaque_-_1992.123_-_Rhode_Island_School_of_Design_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>46 cm</t>
+  </si>
+  <si>
+    <t>38,4 cm</t>
+  </si>
+  <si>
     <t>1937</t>
   </si>
   <si>
@@ -676,6 +724,12 @@
     <t>Huile sur toile (ensemble de 65 panneaux)</t>
   </si>
   <si>
+    <t>1000 cm</t>
+  </si>
+  <si>
+    <t>6000 cm</t>
+  </si>
+  <si>
     <t>Emil</t>
   </si>
   <si>
@@ -697,6 +751,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Filla_Emil%2C_Z%C3%A1ti%C5%A1%C3%AD_s_d%C3%BDmkou_%2C_1934.jpeg/1280px-Filla_Emil%2C_Z%C3%A1ti%C5%A1%C3%AD_s_d%C3%BDmkou_%2C_1934.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>84 cm</t>
+  </si>
+  <si>
     <t>tchèque</t>
   </si>
   <si>
@@ -712,27 +769,42 @@
     <t>1919</t>
   </si>
   <si>
+    <t>Moscou</t>
+  </si>
+  <si>
+    <t>Galerie Tretiakov</t>
+  </si>
+  <si>
+    <t>"Composition (Navires)"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/ce/1919_Filonov_Komposition_Schiffe_anagoria.JPG/1280px-1919_Filonov_Komposition_Schiffe_anagoria.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>156 cm</t>
+  </si>
+  <si>
+    <t>172 cm</t>
+  </si>
+  <si>
+    <t>1920-1921</t>
+  </si>
+  <si>
     <t>Saint-Pétersbourg</t>
   </si>
   <si>
     <t>Musée russe</t>
   </si>
   <si>
-    <t>"Composition (Navires)"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/ce/1919_Filonov_Komposition_Schiffe_anagoria.JPG/1280px-1919_Filonov_Komposition_Schiffe_anagoria.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>1920-1921</t>
-  </si>
-  <si>
     <t>"Formule du prolétariat de Petrograd"</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3d/Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg/1280px-Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>117 cm</t>
+  </si>
+  <si>
     <t>Othon</t>
   </si>
   <si>
@@ -781,6 +853,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Portrait_of_the_Artist%27s_Son_by_Boris_Grigoriev%2C_1920_-_Worcester_Art_Museum_-_IMG_7121.JPG/1280px-Portrait_of_the_Artist%27s_Son_by_Boris_Grigoriev%2C_1920_-_Worcester_Art_Museum_-_IMG_7121.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>92,7 cm</t>
+  </si>
+  <si>
+    <t>73,7 cm</t>
+  </si>
+  <si>
     <t>1922 environ</t>
   </si>
   <si>
@@ -790,6 +868,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d0/Woman_reading_by_Boris_Grigoriev_%28c.1922%2C_MetMuseum%29.jpg/1280px-Woman_reading_by_Boris_Grigoriev_%28c.1922%2C_MetMuseum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>54 cm</t>
+  </si>
+  <si>
+    <t>65,4 cm</t>
+  </si>
+  <si>
     <t>Marsden</t>
   </si>
   <si>
@@ -814,6 +898,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Marsden_Hartley_-_Hall_of_the_Mountain_King_-_2010.94_-_Crystal_Bridges_Museum_of_American_Art.jpg/1280px-Marsden_Hartley_-_Hall_of_the_Mountain_King_-_2010.94_-_Crystal_Bridges_Museum_of_American_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>76,2 cm</t>
+  </si>
+  <si>
     <t>1914</t>
   </si>
   <si>
@@ -886,6 +973,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Gwen_John_-_Self-Portrait.jpg/1280px-Gwen_John_-_Self-Portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>44,8 cm</t>
+  </si>
+  <si>
+    <t>34,9 cm</t>
+  </si>
+  <si>
     <t>anglaise (Royaume-Uni)</t>
   </si>
   <si>
@@ -1012,6 +1105,9 @@
     <t>1891</t>
   </si>
   <si>
+    <t>Taïwan</t>
+  </si>
+  <si>
     <t>Chimei Museum</t>
   </si>
   <si>
@@ -1021,6 +1117,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Moj%C5%BCesz_Kisling_Kiki_de_Montparnasse_1925.jpg/1280px-Moj%C5%BCesz_Kisling_Kiki_de_Montparnasse_1925.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>114 cm</t>
+  </si>
+  <si>
+    <t>79 cm</t>
+  </si>
+  <si>
     <t>polonaise</t>
   </si>
   <si>
@@ -1129,9 +1231,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>84 cm</t>
-  </si>
-  <si>
     <t>42 cm</t>
   </si>
   <si>
@@ -1198,6 +1297,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1d/Bohumil_Kubi%C5%A1ta_-_St_Sebastian.jpg/1280px-Bohumil_Kubi%C5%A1ta_-_St_Sebastian.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>98 cm</t>
+  </si>
+  <si>
+    <t>74,5 cm</t>
+  </si>
+  <si>
     <t>Fernand</t>
   </si>
   <si>
@@ -1282,6 +1387,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f9/Macke_August_Gro%C3%9Fes_Helles_Schaufenster_Sprengel_Museum_01.JPG/1280px-Macke_August_Gro%C3%9Fes_Helles_Schaufenster_Sprengel_Museum_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>106,8 cm</t>
+  </si>
+  <si>
+    <t>82,8 cm</t>
+  </si>
+  <si>
     <t>Neue Pinakothek</t>
   </si>
   <si>
@@ -1306,12 +1417,6 @@
     <t>1935</t>
   </si>
   <si>
-    <t>Moscou</t>
-  </si>
-  <si>
-    <t>Galerie Tretiakov</t>
-  </si>
-  <si>
     <t>"Carré noir sur fond blanc"</t>
   </si>
   <si>
@@ -1363,6 +1468,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/19/Henri_Manguin%2C_1906%2C_Baigneuse_%28Woman_Bather%29%2C_oil_on_canvas%2C_Pushkin_Museum%2C_Moscow.jpg/1280px-Henri_Manguin%2C_1906%2C_Baigneuse_%28Woman_Bather%29%2C_oil_on_canvas%2C_Pushkin_Museum%2C_Moscow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>61 cm</t>
+  </si>
+  <si>
+    <t>49 cm</t>
+  </si>
+  <si>
     <t>Franz</t>
   </si>
   <si>
@@ -1399,6 +1510,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/Marc_Franz_Blaues-Pferdchen_Saarlandmuseum_1912.jpg/1280px-Marc_Franz_Blaues-Pferdchen_Saarlandmuseum_1912.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>57,5 cm</t>
+  </si>
+  <si>
     <t>Albert</t>
   </si>
   <si>
@@ -1423,9 +1537,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2d/Notre_Dame_2_Albert_Marquet_%281904%29.jpg/1280px-Notre_Dame_2_Albert_Marquet_%281904%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>46 cm</t>
-  </si>
-  <si>
     <t>33 cm</t>
   </si>
   <si>
@@ -1453,6 +1564,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Bay_of_Naples_Albert_Marquet_%281908%29.jpg/1280px-Bay_of_Naples_Albert_Marquet_%281908%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>76,5 cm</t>
+  </si>
+  <si>
     <t>"La Femme blonde"</t>
   </si>
   <si>
@@ -1555,6 +1669,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Amedeo_Modigliani%2C_Woman_with_Red_Hair%2C_1917%2C_NGA_46651.jpg/1280px-Amedeo_Modigliani%2C_Woman_with_Red_Hair%2C_1917%2C_NGA_46651.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>92,1 cm</t>
+  </si>
+  <si>
+    <t>60,7 cm</t>
+  </si>
+  <si>
     <t>"Garçon en costume marin"</t>
   </si>
   <si>
@@ -1588,6 +1708,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG/960px-Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
+    <t>135,5 cm</t>
+  </si>
+  <si>
+    <t>115 cm</t>
+  </si>
+  <si>
     <t>hongroise</t>
   </si>
   <si>
@@ -1645,6 +1771,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/40/Otto_Mueller_-_Drei_Akte_in_Landschaft_-_ca1919.jpeg/1280px-Otto_Mueller_-_Drei_Akte_in_Landschaft_-_ca1919.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>88,5 cm</t>
+  </si>
+  <si>
     <t>Edvard</t>
   </si>
   <si>
@@ -1747,9 +1876,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Christopher_richard_wynne_nevinson%2C_la_mitrailleuse%2C_1915.jpg/1280px-Christopher_richard_wynne_nevinson%2C_la_mitrailleuse%2C_1915.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>61 cm</t>
-  </si>
-  <si>
     <t>50,8 cm</t>
   </si>
   <si>
@@ -1786,12 +1912,21 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e7/Jules_Pascin_-_La_M%C3%A9lancolique_-_2002.156_-_Museum_of_Fine_Arts.jpg/1280px-Jules_Pascin_-_La_M%C3%A9lancolique_-_2002.156_-_Museum_of_Fine_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>71,1 cm</t>
+  </si>
+  <si>
+    <t>58,4 cm</t>
+  </si>
+  <si>
     <t>bulgare</t>
   </si>
   <si>
     <t>1928</t>
   </si>
   <si>
+    <t>Saitama, Japon</t>
+  </si>
+  <si>
     <t>Musée d'Art moderne</t>
   </si>
   <si>
@@ -1801,6 +1936,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/JulesPascin-1928-Sleeping_Naked_Girl.png/1280px-JulesPascin-1928-Sleeping_Naked_Girl.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>92,5 cm</t>
+  </si>
+  <si>
     <t>Francis</t>
   </si>
   <si>
@@ -1846,6 +1984,12 @@
     <t>Tempera sur carton</t>
   </si>
   <si>
+    <t>85 cm</t>
+  </si>
+  <si>
+    <t>112,5 cm</t>
+  </si>
+  <si>
     <t>ROUSSEAU</t>
   </si>
   <si>
@@ -1906,18 +2050,21 @@
     <t>298,5 cm</t>
   </si>
   <si>
+    <t>431,5 cm</t>
+  </si>
+  <si>
+    <t>ROUSSEL</t>
+  </si>
+  <si>
+    <t>"L'Enlèvement des filles de Leucippe"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG/960px-Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Ker-Xavier</t>
   </si>
   <si>
-    <t>ROUSSEL</t>
-  </si>
-  <si>
-    <t>"L'Enlèvement des filles de Leucippe"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG/960px-Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>1930 environ</t>
   </si>
   <si>
@@ -1927,6 +2074,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Ker-Xavier_Roussel_-_Devant_la_mer_%28Varengeville%29_-_PPP633_-_Mus%C3%A9e_des_Beaux-Arts_de_la_ville_de_Paris.jpg/1280px-Ker-Xavier_Roussel_-_Devant_la_mer_%28Varengeville%29_-_PPP633_-_Mus%C3%A9e_des_Beaux-Arts_de_la_ville_de_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>81,5 cm</t>
+  </si>
+  <si>
     <t>Egon</t>
   </si>
   <si>
@@ -2038,9 +2188,6 @@
     <t>202 cm</t>
   </si>
   <si>
-    <t>114 cm</t>
-  </si>
-  <si>
     <t>biélorusse</t>
   </si>
   <si>
@@ -2053,6 +2200,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/Chaim_Soutine_-_Carcass_of_Beef_-_57.12_-_Minneapolis_Institute_of_Arts.jpg/1280px-Chaim_Soutine_-_Carcass_of_Beef_-_57.12_-_Minneapolis_Institute_of_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>116,2 cm</t>
+  </si>
+  <si>
     <t>1925 environ</t>
   </si>
   <si>
@@ -2065,6 +2215,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Carcass_of_Beef_by_Chaim_Soutine%2C_c._1925%2C_Albright-Knox_Art_Gallery.jpg/1280px-Carcass_of_Beef_by_Chaim_Soutine%2C_c._1925%2C_Albright-Knox_Art_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>130,9 cm</t>
+  </si>
+  <si>
+    <t>98,1 cm</t>
+  </si>
+  <si>
     <t>"Le Groom"</t>
   </si>
   <si>
@@ -2095,9 +2251,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Mama%2C_Papa_is_Wounded%21.jpg/960px-Mama%2C_Papa_is_Wounded%21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>92,1 cm</t>
-  </si>
-  <si>
     <t>"Divisibilité indéfinie"</t>
   </si>
   <si>
@@ -2131,12 +2284,18 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg/1280px-Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>121 cm</t>
+  </si>
+  <si>
     <t>"Rue du Mont-Cenis"</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Maurice_Utrillo._Rue_du_Mont-Cenis._1914._Mus%C3%A9e_de_l%27Orangerie.jpg/1280px-Maurice_Utrillo._Rue_du_Mont-Cenis._1914._Mus%C3%A9e_de_l%27Orangerie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>107 cm</t>
+  </si>
+  <si>
     <t>Suzanne</t>
   </si>
   <si>
@@ -2188,9 +2347,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/%28Barcelona%29_Portrait_de_famille_-_Suzanne_Valadon_%281912%29.jpg/960px-%28Barcelona%29_Portrait_de_famille_-_Suzanne_Valadon_%281912%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>98 cm</t>
-  </si>
-  <si>
     <t>Louis</t>
   </si>
   <si>
@@ -2227,9 +2383,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/ff/Theo_van_doesburg_de_koe.jpg/1280px-Theo_van_doesburg_de_koe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>37,5 cm</t>
-  </si>
-  <si>
     <t>Alexej</t>
   </si>
   <si>
@@ -2245,6 +2398,18 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/85/Alexej_von_Jawlensky_-_Selbstbildnis_1912.jpg/1280px-Alexej_von_Jawlensky_-_Selbstbildnis_1912.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>53,5  cm</t>
+  </si>
+  <si>
+    <t>48,5 cm</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Art Institute</t>
+  </si>
+  <si>
     <t>"Tête mystique"</t>
   </si>
   <si>
@@ -2269,15 +2434,27 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Werefkin%2C_Marianne_von_-_Selfportrait_I_-_Google_Art_Project.jpg/1280px-Werefkin%2C_Marianne_von_-_Selfportrait_I_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>51 cm</t>
+  </si>
+  <si>
     <t>WOOD</t>
   </si>
   <si>
+    <t>Cambridge, Uk</t>
+  </si>
+  <si>
+    <t>Kettle's Yard</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/Christopher_Wood_Autoportrait_1927.jpg/1280px-Christopher_Wood_Autoportrait_1927.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>Grant</t>
   </si>
   <si>
+    <t xml:space="preserve">Art Institute </t>
+  </si>
+  <si>
     <t>"American Gothic"</t>
   </si>
   <si>
@@ -2293,199 +2470,19 @@
     <t>65,3 cm</t>
   </si>
   <si>
+    <t xml:space="preserve">Cincinnati </t>
+  </si>
+  <si>
+    <t>Art Museum</t>
+  </si>
+  <si>
     <t>"Daughters of Revolution"</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c9/Daughters_of_Revolution_by_Grant_Wood%2C_1932.jpg/1280px-Daughters_of_Revolution_by_Grant_Wood%2C_1932.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>GRIS</t>
-  </si>
-  <si>
-    <t>116,5 cm</t>
-  </si>
-  <si>
-    <t>89,2 cm</t>
-  </si>
-  <si>
-    <t>25 cm</t>
-  </si>
-  <si>
-    <t>32,8 cm</t>
-  </si>
-  <si>
-    <t>34 cm</t>
-  </si>
-  <si>
-    <t>21 cm</t>
-  </si>
-  <si>
-    <t>124,5 cm</t>
-  </si>
-  <si>
-    <t>109 cm</t>
-  </si>
-  <si>
-    <t>54,5 cm</t>
-  </si>
-  <si>
-    <t>90,4 cm</t>
-  </si>
-  <si>
-    <t>70,4 cm</t>
-  </si>
-  <si>
-    <t>170 cm</t>
-  </si>
-  <si>
-    <t>104 cm</t>
-  </si>
-  <si>
-    <t>38,4 cm</t>
-  </si>
-  <si>
-    <t>1000 cm</t>
-  </si>
-  <si>
-    <t>6000 cm</t>
-  </si>
-  <si>
-    <t>156 cm</t>
-  </si>
-  <si>
-    <t>172 cm</t>
-  </si>
-  <si>
-    <t>117 cm</t>
-  </si>
-  <si>
-    <t>92,7 cm</t>
-  </si>
-  <si>
-    <t>73,7 cm</t>
-  </si>
-  <si>
-    <t>54 cm</t>
-  </si>
-  <si>
-    <t>65,4 cm</t>
-  </si>
-  <si>
-    <t>76,2 cm</t>
-  </si>
-  <si>
-    <t>44,8 cm</t>
-  </si>
-  <si>
-    <t>34,9 cm</t>
-  </si>
-  <si>
-    <t>Taïwan</t>
-  </si>
-  <si>
-    <t>79 cm</t>
-  </si>
-  <si>
-    <t>74,5 cm</t>
-  </si>
-  <si>
-    <t>106,8 cm</t>
-  </si>
-  <si>
-    <t>82,8 cm</t>
-  </si>
-  <si>
-    <t>49 cm</t>
-  </si>
-  <si>
-    <t>57,5 cm</t>
-  </si>
-  <si>
-    <t>76,5 cm</t>
-  </si>
-  <si>
-    <t>60,7 cm</t>
-  </si>
-  <si>
-    <t>135,5 cm</t>
-  </si>
-  <si>
-    <t>115 cm</t>
-  </si>
-  <si>
-    <t>88,5 cm</t>
-  </si>
-  <si>
-    <t>71,1 cm</t>
-  </si>
-  <si>
-    <t>58,4 cm</t>
-  </si>
-  <si>
-    <t>Saitama, Japon</t>
-  </si>
-  <si>
-    <t>92,5 cm</t>
-  </si>
-  <si>
-    <t>85 cm</t>
-  </si>
-  <si>
-    <t>112,5 cm</t>
-  </si>
-  <si>
-    <t>431,5 cm</t>
-  </si>
-  <si>
-    <t>81,5 cm</t>
-  </si>
-  <si>
-    <t>116,2 cm</t>
-  </si>
-  <si>
-    <t>130,9 cm</t>
-  </si>
-  <si>
-    <t>98,1 cm</t>
-  </si>
-  <si>
-    <t>121 cm</t>
-  </si>
-  <si>
-    <t>107 cm</t>
-  </si>
-  <si>
-    <t>53,5  cm</t>
-  </si>
-  <si>
-    <t>48,5 cm</t>
-  </si>
-  <si>
-    <t>51 cm</t>
-  </si>
-  <si>
-    <t>Cambridge, Uk</t>
-  </si>
-  <si>
-    <t>Kettle's Yard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art Institute </t>
-  </si>
-  <si>
-    <t>Chicago</t>
-  </si>
-  <si>
-    <t>Art Museum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cincinnati </t>
-  </si>
-  <si>
-    <t>Art Institute</t>
+    <t>Juan GRIS</t>
   </si>
 </sst>
 </file>
@@ -2963,11 +2960,8 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>759</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>24</v>
@@ -3004,11 +2998,8 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>759</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
@@ -3048,11 +3039,8 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>759</v>
-      </c>
       <c r="B4" s="2" t="s">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>24</v>
@@ -3079,10 +3067,10 @@
         <v>30</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>761</v>
+        <v>44</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>762</v>
+        <v>45</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>33</v>
@@ -3092,11 +3080,8 @@
       </c>
     </row>
     <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>759</v>
-      </c>
       <c r="B5" s="2" t="s">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>24</v>
@@ -3105,25 +3090,25 @@
         <v>25</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>763</v>
+        <v>50</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>764</v>
+        <v>51</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>33</v>
@@ -3134,43 +3119,43 @@
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="X6" s="2">
         <v>1</v>
@@ -3178,43 +3163,43 @@
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="T7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="X7" s="2">
         <v>3</v>
@@ -3222,43 +3207,43 @@
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>765</v>
+        <v>79</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>766</v>
+        <v>80</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X8" s="2">
         <v>2</v>
@@ -3266,43 +3251,43 @@
     </row>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X9" s="2">
         <v>3</v>
@@ -3310,43 +3295,43 @@
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="U10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="W10" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="X10" s="2">
         <v>1</v>
@@ -3354,19 +3339,19 @@
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>35</v>
@@ -3375,22 +3360,22 @@
         <v>36</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X11" s="2">
         <v>3</v>
@@ -3398,19 +3383,19 @@
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>35</v>
@@ -3419,22 +3404,22 @@
         <v>36</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="X12" s="2">
         <v>1</v>
@@ -3442,19 +3427,19 @@
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>35</v>
@@ -3463,22 +3448,22 @@
         <v>36</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="X13" s="2">
         <v>3</v>
@@ -3486,43 +3471,43 @@
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>767</v>
+        <v>129</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>768</v>
+        <v>130</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X14" s="2">
         <v>3</v>
@@ -3530,19 +3515,19 @@
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>35</v>
@@ -3551,22 +3536,22 @@
         <v>36</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X15" s="2">
         <v>3</v>
@@ -3574,40 +3559,40 @@
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="W16" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="X16" s="2">
         <v>1</v>
@@ -3615,43 +3600,43 @@
     </row>
     <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>769</v>
+        <v>147</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>735</v>
+        <v>148</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X17" s="2">
         <v>3</v>
@@ -3659,43 +3644,43 @@
     </row>
     <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>770</v>
+        <v>157</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>771</v>
+        <v>158</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X18" s="2">
         <v>3</v>
@@ -3703,43 +3688,43 @@
     </row>
     <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X19" s="2">
         <v>2</v>
@@ -3747,43 +3732,43 @@
     </row>
     <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X20" s="2">
         <v>1</v>
@@ -3791,40 +3776,40 @@
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X21" s="2">
         <v>3</v>
@@ -3832,40 +3817,40 @@
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>772</v>
+        <v>187</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>773</v>
+        <v>188</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X22" s="2">
         <v>1</v>
@@ -3873,31 +3858,31 @@
     </row>
     <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>30</v>
@@ -3906,10 +3891,10 @@
         <v>40</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X23" s="2">
         <v>3</v>
@@ -3917,43 +3902,43 @@
     </row>
     <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X24" s="2">
         <v>3</v>
@@ -3961,43 +3946,43 @@
     </row>
     <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X25" s="2">
         <v>1</v>
@@ -4005,19 +3990,19 @@
     </row>
     <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B26" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>35</v>
@@ -4026,22 +4011,22 @@
         <v>41</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="X26" s="2">
         <v>2</v>
@@ -4049,19 +4034,19 @@
     </row>
     <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>35</v>
@@ -4070,22 +4055,22 @@
         <v>41</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="X27" s="2">
         <v>3</v>
@@ -4093,43 +4078,43 @@
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B28" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>467</v>
+        <v>228</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>774</v>
+        <v>229</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X28" s="2">
         <v>3</v>
@@ -4137,40 +4122,40 @@
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>775</v>
+        <v>234</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>776</v>
+        <v>235</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X29" s="2">
         <v>1</v>
@@ -4178,43 +4163,43 @@
     </row>
     <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>773</v>
+        <v>188</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>369</v>
+        <v>243</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="X30" s="2">
         <v>2</v>
@@ -4222,43 +4207,43 @@
     </row>
     <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B31" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>428</v>
+        <v>249</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>429</v>
+        <v>250</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>777</v>
+        <v>253</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>778</v>
+        <v>254</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X31" s="2">
         <v>3</v>
@@ -4266,43 +4251,43 @@
     </row>
     <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B32" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>779</v>
+        <v>260</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X32" s="2">
         <v>1</v>
@@ -4310,43 +4295,43 @@
     </row>
     <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X33" s="2">
         <v>2</v>
@@ -4354,40 +4339,40 @@
     </row>
     <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>780</v>
+        <v>277</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>781</v>
+        <v>278</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X34" s="2">
         <v>3</v>
@@ -4395,19 +4380,19 @@
     </row>
     <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>35</v>
@@ -4416,22 +4401,22 @@
         <v>41</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>782</v>
+        <v>282</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>783</v>
+        <v>283</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X35" s="2">
         <v>2</v>
@@ -4439,43 +4424,43 @@
     </row>
     <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>784</v>
+        <v>292</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>784</v>
+        <v>292</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="X36" s="2">
         <v>3</v>
@@ -4483,19 +4468,19 @@
     </row>
     <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>35</v>
@@ -4504,22 +4489,22 @@
         <v>41</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="X37" s="2">
         <v>2</v>
@@ -4527,43 +4512,43 @@
     </row>
     <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="X38" s="2">
         <v>1</v>
@@ -4571,43 +4556,43 @@
     </row>
     <row r="39" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>785</v>
+        <v>317</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>786</v>
+        <v>318</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="X39" s="2">
         <v>2</v>
@@ -4615,43 +4600,43 @@
     </row>
     <row r="40" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="X40" s="2">
         <v>1</v>
@@ -4659,43 +4644,43 @@
     </row>
     <row r="41" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X41" s="2">
         <v>3</v>
@@ -4703,43 +4688,43 @@
     </row>
     <row r="42" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X42" s="2">
         <v>1</v>
@@ -4747,43 +4732,43 @@
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X43" s="2">
         <v>3</v>
@@ -4791,43 +4776,43 @@
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X44" s="2">
         <v>3</v>
@@ -4835,19 +4820,19 @@
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>35</v>
@@ -4856,22 +4841,22 @@
         <v>36</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="U45" s="2" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X45" s="2">
         <v>1</v>
@@ -4879,43 +4864,43 @@
     </row>
     <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>787</v>
+        <v>361</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>672</v>
+        <v>365</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>788</v>
+        <v>366</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="X46" s="2">
         <v>2</v>
@@ -4923,43 +4908,43 @@
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="X47" s="2">
         <v>2</v>
@@ -4967,19 +4952,19 @@
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>35</v>
@@ -4988,22 +4973,22 @@
         <v>36</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="X48" s="2">
         <v>3</v>
@@ -5011,40 +4996,40 @@
     </row>
     <row r="49" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="X49" s="2">
         <v>3</v>
@@ -5052,43 +5037,43 @@
     </row>
     <row r="50" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="X50" s="2">
         <v>3</v>
@@ -5096,43 +5081,43 @@
     </row>
     <row r="51" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>369</v>
+        <v>243</v>
       </c>
       <c r="U51" s="2" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="X51" s="2">
         <v>3</v>
@@ -5140,46 +5125,46 @@
     </row>
     <row r="52" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="X52" s="2">
         <v>1</v>
@@ -5187,46 +5172,46 @@
     </row>
     <row r="53" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>382</v>
+        <v>415</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="X53" s="2">
         <v>3</v>
@@ -5234,43 +5219,43 @@
     </row>
     <row r="54" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s">
-        <v>385</v>
+        <v>418</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>386</v>
+        <v>419</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="U54" s="2" t="s">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="X54" s="2">
         <v>2</v>
@@ -5278,43 +5263,43 @@
     </row>
     <row r="55" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s">
-        <v>385</v>
+        <v>418</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>722</v>
+        <v>425</v>
       </c>
       <c r="U55" s="2" t="s">
-        <v>789</v>
+        <v>426</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="X55" s="2">
         <v>3</v>
@@ -5322,40 +5307,40 @@
     </row>
     <row r="56" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X56" s="2">
         <v>1</v>
@@ -5363,40 +5348,40 @@
     </row>
     <row r="57" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>401</v>
+        <v>436</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>402</v>
+        <v>437</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X57" s="2">
         <v>3</v>
@@ -5404,43 +5389,43 @@
     </row>
     <row r="58" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X58" s="2">
         <v>3</v>
@@ -5448,19 +5433,19 @@
     </row>
     <row r="59" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>35</v>
@@ -5469,22 +5454,22 @@
         <v>36</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="S59" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>413</v>
+        <v>448</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X59" s="2">
         <v>3</v>
@@ -5492,43 +5477,43 @@
     </row>
     <row r="60" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>416</v>
+        <v>451</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>417</v>
+        <v>452</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>418</v>
+        <v>453</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>790</v>
+        <v>455</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>791</v>
+        <v>456</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X60" s="2">
         <v>3</v>
@@ -5536,43 +5521,43 @@
     </row>
     <row r="61" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>423</v>
+        <v>460</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X61" s="2">
         <v>1</v>
@@ -5580,43 +5565,43 @@
     </row>
     <row r="62" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>34</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>428</v>
+        <v>249</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>429</v>
+        <v>250</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X62" s="2">
         <v>1</v>
@@ -5624,19 +5609,19 @@
     </row>
     <row r="63" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>35</v>
@@ -5645,22 +5630,22 @@
         <v>36</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X63" s="2">
         <v>3</v>
@@ -5668,43 +5653,43 @@
     </row>
     <row r="64" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s">
-        <v>437</v>
+        <v>472</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>439</v>
+        <v>474</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X64" s="2">
         <v>2</v>
@@ -5712,43 +5697,43 @@
     </row>
     <row r="65" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B65" t="s">
-        <v>437</v>
+        <v>472</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>428</v>
+        <v>249</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>575</v>
+        <v>482</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>792</v>
+        <v>483</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X65" s="2">
         <v>3</v>
@@ -5756,43 +5741,43 @@
     </row>
     <row r="66" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X66" s="2">
         <v>1</v>
@@ -5800,43 +5785,43 @@
     </row>
     <row r="67" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="B67" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>793</v>
+        <v>496</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X67" s="2">
         <v>3</v>
@@ -5844,43 +5829,43 @@
     </row>
     <row r="68" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>466</v>
+        <v>504</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>467</v>
+        <v>228</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X68" s="2">
         <v>2</v>
@@ -5888,43 +5873,43 @@
     </row>
     <row r="69" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B69" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>472</v>
+        <v>509</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X69" s="2">
         <v>3</v>
@@ -5932,43 +5917,43 @@
     </row>
     <row r="70" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="U70" s="2" t="s">
-        <v>794</v>
+        <v>514</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X70" s="2">
         <v>3</v>
@@ -5976,43 +5961,43 @@
     </row>
     <row r="71" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>477</v>
+        <v>515</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>479</v>
+        <v>517</v>
       </c>
       <c r="U71" s="2" t="s">
-        <v>479</v>
+        <v>517</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X71" s="2">
         <v>3</v>
@@ -6020,43 +6005,43 @@
     </row>
     <row r="72" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>482</v>
+        <v>520</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>483</v>
+        <v>521</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>484</v>
+        <v>522</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>485</v>
+        <v>523</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="U72" s="2" t="s">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X72" s="2">
         <v>3</v>
@@ -6064,40 +6049,40 @@
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="U73" s="2" t="s">
-        <v>493</v>
+        <v>531</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X73" s="2">
         <v>3</v>
@@ -6105,43 +6090,43 @@
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="M74" s="4" t="s">
-        <v>494</v>
+        <v>532</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>495</v>
+        <v>533</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>496</v>
+        <v>534</v>
       </c>
       <c r="U74" s="2" t="s">
-        <v>467</v>
+        <v>228</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X74" s="2">
         <v>3</v>
@@ -6149,43 +6134,43 @@
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>497</v>
+        <v>535</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>498</v>
+        <v>536</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X75" s="2">
         <v>1</v>
@@ -6193,34 +6178,34 @@
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="B76" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>30</v>
@@ -6229,10 +6214,10 @@
         <v>40</v>
       </c>
       <c r="U76" s="2" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="X76" s="2">
         <v>1</v>
@@ -6240,43 +6225,43 @@
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="B77" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>691</v>
+        <v>549</v>
       </c>
       <c r="U77" s="2" t="s">
-        <v>795</v>
+        <v>550</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="X77" s="2">
         <v>3</v>
@@ -6284,43 +6269,43 @@
     </row>
     <row r="78" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="B78" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>483</v>
+        <v>521</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>484</v>
+        <v>522</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>511</v>
+        <v>551</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>512</v>
+        <v>552</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="U78" s="2" t="s">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="X78" s="2">
         <v>3</v>
@@ -6328,19 +6313,19 @@
     </row>
     <row r="79" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="B79" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>35</v>
@@ -6349,22 +6334,22 @@
         <v>41</v>
       </c>
       <c r="M79" s="4" t="s">
-        <v>513</v>
+        <v>553</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>514</v>
+        <v>554</v>
       </c>
       <c r="S79" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>515</v>
+        <v>555</v>
       </c>
       <c r="U79" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="W79" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="X79" s="2">
         <v>3</v>
@@ -6372,43 +6357,43 @@
     </row>
     <row r="80" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>516</v>
+        <v>556</v>
       </c>
       <c r="B80" t="s">
-        <v>517</v>
+        <v>557</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>518</v>
+        <v>558</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>519</v>
+        <v>559</v>
       </c>
       <c r="M80" s="4" t="s">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="S80" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>796</v>
+        <v>562</v>
       </c>
       <c r="U80" s="2" t="s">
-        <v>797</v>
+        <v>563</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>522</v>
+        <v>564</v>
       </c>
       <c r="X80" s="2">
         <v>1</v>
@@ -6416,43 +6401,43 @@
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>523</v>
+        <v>565</v>
       </c>
       <c r="B81" t="s">
-        <v>524</v>
+        <v>566</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>525</v>
+        <v>567</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>526</v>
+        <v>568</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>527</v>
+        <v>569</v>
       </c>
       <c r="M81" s="4" t="s">
-        <v>528</v>
+        <v>570</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>529</v>
+        <v>571</v>
       </c>
       <c r="S81" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>467</v>
+        <v>228</v>
       </c>
       <c r="U81" s="2" t="s">
-        <v>467</v>
+        <v>228</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>530</v>
+        <v>572</v>
       </c>
       <c r="X81" s="2">
         <v>1</v>
@@ -6460,19 +6445,19 @@
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>523</v>
+        <v>565</v>
       </c>
       <c r="B82" t="s">
-        <v>524</v>
+        <v>566</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>525</v>
+        <v>567</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>531</v>
+        <v>573</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>35</v>
@@ -6481,22 +6466,22 @@
         <v>36</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>532</v>
+        <v>574</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>533</v>
+        <v>575</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>534</v>
+        <v>576</v>
       </c>
       <c r="U82" s="2" t="s">
-        <v>534</v>
+        <v>576</v>
       </c>
       <c r="W82" s="1" t="s">
-        <v>530</v>
+        <v>572</v>
       </c>
       <c r="X82" s="2">
         <v>3</v>
@@ -6504,43 +6489,43 @@
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>535</v>
+        <v>577</v>
       </c>
       <c r="B83" t="s">
-        <v>536</v>
+        <v>578</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>538</v>
+        <v>580</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>539</v>
+        <v>581</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>540</v>
+        <v>582</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T83" s="2" t="s">
-        <v>798</v>
+        <v>583</v>
       </c>
       <c r="U83" s="2" t="s">
-        <v>423</v>
+        <v>460</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X83" s="2">
         <v>2</v>
@@ -6548,43 +6533,43 @@
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>541</v>
+        <v>584</v>
       </c>
       <c r="B84" t="s">
-        <v>542</v>
+        <v>585</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>543</v>
+        <v>586</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>544</v>
+        <v>587</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>545</v>
+        <v>588</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>546</v>
+        <v>589</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>547</v>
+        <v>590</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="U84" s="2" t="s">
-        <v>548</v>
+        <v>591</v>
       </c>
       <c r="W84" s="1" t="s">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="X84" s="2">
         <v>3</v>
@@ -6592,46 +6577,46 @@
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>541</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s">
-        <v>542</v>
+        <v>585</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>543</v>
+        <v>586</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>551</v>
+        <v>594</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>552</v>
+        <v>595</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>553</v>
+        <v>596</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>554</v>
+        <v>597</v>
       </c>
       <c r="S85" s="1" t="s">
-        <v>555</v>
+        <v>598</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>556</v>
+        <v>599</v>
       </c>
       <c r="U85" s="2" t="s">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="X85" s="2">
         <v>1</v>
@@ -6639,46 +6624,46 @@
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>541</v>
+        <v>584</v>
       </c>
       <c r="B86" t="s">
-        <v>542</v>
+        <v>585</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>543</v>
+        <v>586</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>559</v>
+        <v>602</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>560</v>
+        <v>603</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>561</v>
+        <v>604</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="U86" s="2" t="s">
-        <v>562</v>
+        <v>605</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="X86" s="2">
         <v>3</v>
@@ -6686,43 +6671,43 @@
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="B87" t="s">
-        <v>563</v>
+        <v>606</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>564</v>
+        <v>607</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>565</v>
+        <v>608</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>566</v>
+        <v>609</v>
       </c>
       <c r="M87" s="4" t="s">
-        <v>567</v>
+        <v>610</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>568</v>
+        <v>611</v>
       </c>
       <c r="S87" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>569</v>
+        <v>612</v>
       </c>
       <c r="U87" s="2" t="s">
-        <v>570</v>
+        <v>613</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="X87" s="2">
         <v>2</v>
@@ -6730,43 +6715,43 @@
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>571</v>
+        <v>614</v>
       </c>
       <c r="B88" t="s">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>564</v>
+        <v>607</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>34</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>573</v>
+        <v>616</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>574</v>
+        <v>617</v>
       </c>
       <c r="S88" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>575</v>
+        <v>482</v>
       </c>
       <c r="U88" s="2" t="s">
-        <v>576</v>
+        <v>618</v>
       </c>
       <c r="W88" s="1" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="X88" s="2">
         <v>2</v>
@@ -6774,43 +6759,43 @@
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>571</v>
+        <v>614</v>
       </c>
       <c r="B89" t="s">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>564</v>
+        <v>607</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>578</v>
+        <v>620</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>579</v>
+        <v>621</v>
       </c>
       <c r="S89" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T89" s="2" t="s">
-        <v>580</v>
+        <v>622</v>
       </c>
       <c r="U89" s="2" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="X89" s="2">
         <v>3</v>
@@ -6818,43 +6803,43 @@
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>582</v>
+        <v>624</v>
       </c>
       <c r="B90" t="s">
-        <v>583</v>
+        <v>625</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="H90" s="2">
         <v>1909</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>584</v>
+        <v>626</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>585</v>
+        <v>627</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>586</v>
+        <v>628</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>587</v>
+        <v>629</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T90" s="2" t="s">
-        <v>799</v>
+        <v>630</v>
       </c>
       <c r="U90" s="2" t="s">
-        <v>800</v>
+        <v>631</v>
       </c>
       <c r="W90" s="1" t="s">
-        <v>588</v>
+        <v>632</v>
       </c>
       <c r="X90" s="2">
         <v>3</v>
@@ -6862,43 +6847,43 @@
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>582</v>
+        <v>624</v>
       </c>
       <c r="B91" t="s">
-        <v>583</v>
+        <v>625</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>801</v>
+        <v>634</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>591</v>
+        <v>636</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>592</v>
+        <v>637</v>
       </c>
       <c r="S91" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T91" s="2" t="s">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="U91" s="2" t="s">
-        <v>802</v>
+        <v>638</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>588</v>
+        <v>632</v>
       </c>
       <c r="X91" s="2">
         <v>2</v>
@@ -6906,43 +6891,43 @@
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>593</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s">
-        <v>594</v>
+        <v>640</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>595</v>
+        <v>641</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>596</v>
+        <v>642</v>
       </c>
       <c r="S92" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>597</v>
+        <v>643</v>
       </c>
       <c r="U92" s="2" t="s">
-        <v>598</v>
+        <v>644</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X92" s="2">
         <v>2</v>
@@ -6950,43 +6935,43 @@
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>593</v>
+        <v>639</v>
       </c>
       <c r="B93" t="s">
-        <v>594</v>
+        <v>640</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>599</v>
+        <v>645</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>600</v>
+        <v>646</v>
       </c>
       <c r="S93" s="1" t="s">
-        <v>601</v>
+        <v>647</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>602</v>
+        <v>648</v>
       </c>
       <c r="U93" s="2" t="s">
-        <v>603</v>
+        <v>649</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X93" s="2">
         <v>3</v>
@@ -6994,43 +6979,43 @@
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B94" t="s">
-        <v>604</v>
+        <v>650</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>428</v>
+        <v>249</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>429</v>
+        <v>250</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>605</v>
+        <v>651</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>606</v>
+        <v>652</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>607</v>
+        <v>653</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>803</v>
+        <v>654</v>
       </c>
       <c r="U94" s="2" t="s">
-        <v>804</v>
+        <v>655</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X94" s="2">
         <v>2</v>
@@ -7038,25 +7023,25 @@
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B95" t="s">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>611</v>
+        <v>659</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>35</v>
@@ -7065,22 +7050,22 @@
         <v>36</v>
       </c>
       <c r="M95" s="4" t="s">
-        <v>612</v>
+        <v>660</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>613</v>
+        <v>661</v>
       </c>
       <c r="S95" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="U95" s="2" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X95" s="2">
         <v>3</v>
@@ -7088,49 +7073,49 @@
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B96" t="s">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M96" s="4" t="s">
-        <v>616</v>
+        <v>664</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>617</v>
+        <v>665</v>
       </c>
       <c r="S96" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T96" s="2" t="s">
-        <v>618</v>
+        <v>666</v>
       </c>
       <c r="U96" s="2" t="s">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X96" s="2">
         <v>3</v>
@@ -7138,49 +7123,49 @@
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B97" t="s">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="M97" s="4" t="s">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>621</v>
+        <v>669</v>
       </c>
       <c r="S97" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>622</v>
+        <v>670</v>
       </c>
       <c r="U97" s="2" t="s">
-        <v>623</v>
+        <v>671</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X97" s="2">
         <v>3</v>
@@ -7188,25 +7173,25 @@
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="B98" t="s">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>35</v>
@@ -7215,22 +7200,22 @@
         <v>36</v>
       </c>
       <c r="M98" s="4" t="s">
-        <v>624</v>
+        <v>672</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>625</v>
+        <v>673</v>
       </c>
       <c r="S98" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>626</v>
+        <v>674</v>
       </c>
       <c r="U98" s="2" t="s">
-        <v>627</v>
+        <v>675</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X98" s="2">
         <v>1</v>
@@ -7238,43 +7223,43 @@
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>805</v>
+        <v>676</v>
       </c>
       <c r="B99" t="s">
-        <v>629</v>
+        <v>677</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M99" s="4" t="s">
-        <v>630</v>
+        <v>678</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>631</v>
+        <v>679</v>
       </c>
       <c r="S99" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T99" s="2" t="s">
-        <v>805</v>
+        <v>676</v>
       </c>
       <c r="U99" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X99" s="2">
         <v>2</v>
@@ -7282,40 +7267,40 @@
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>628</v>
+        <v>680</v>
       </c>
       <c r="B100" t="s">
-        <v>629</v>
+        <v>677</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>632</v>
+        <v>681</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>633</v>
+        <v>682</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>634</v>
+        <v>683</v>
       </c>
       <c r="S100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T100" s="2" t="s">
-        <v>806</v>
+        <v>684</v>
       </c>
       <c r="U100" s="2" t="s">
-        <v>761</v>
+        <v>44</v>
       </c>
       <c r="W100" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X100" s="2">
         <v>3</v>
@@ -7323,43 +7308,43 @@
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>635</v>
+        <v>685</v>
       </c>
       <c r="B101" t="s">
-        <v>636</v>
+        <v>686</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>637</v>
+        <v>687</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>638</v>
+        <v>688</v>
       </c>
       <c r="M101" s="4" t="s">
-        <v>639</v>
+        <v>689</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>640</v>
+        <v>690</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>641</v>
+        <v>691</v>
       </c>
       <c r="T101" s="2" t="s">
-        <v>642</v>
+        <v>692</v>
       </c>
       <c r="U101" s="2" t="s">
-        <v>643</v>
+        <v>693</v>
       </c>
       <c r="W101" s="1" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="X101" s="2">
         <v>1</v>
@@ -7367,43 +7352,43 @@
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>635</v>
+        <v>685</v>
       </c>
       <c r="B102" t="s">
-        <v>636</v>
+        <v>686</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>637</v>
+        <v>687</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>638</v>
+        <v>688</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>644</v>
+        <v>694</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>645</v>
+        <v>695</v>
       </c>
       <c r="S102" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T102" s="2" t="s">
-        <v>646</v>
+        <v>696</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>647</v>
+        <v>697</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="X102" s="2">
         <v>3</v>
@@ -7411,43 +7396,43 @@
     </row>
     <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>635</v>
+        <v>685</v>
       </c>
       <c r="B103" t="s">
-        <v>636</v>
+        <v>686</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>637</v>
+        <v>687</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>34</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>648</v>
+        <v>698</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="S103" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T103" s="2" t="s">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="U103" s="2" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="X103" s="2">
         <v>3</v>
@@ -7455,43 +7440,43 @@
     </row>
     <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>635</v>
+        <v>685</v>
       </c>
       <c r="B104" t="s">
-        <v>636</v>
+        <v>686</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>637</v>
+        <v>687</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="M104" s="4" t="s">
-        <v>651</v>
+        <v>701</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>652</v>
+        <v>702</v>
       </c>
       <c r="S104" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T104" s="2" t="s">
-        <v>653</v>
+        <v>703</v>
       </c>
       <c r="U104" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="X104" s="2">
         <v>3</v>
@@ -7499,43 +7484,43 @@
     </row>
     <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>654</v>
+        <v>704</v>
       </c>
       <c r="B105" t="s">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>656</v>
+        <v>706</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>658</v>
+        <v>708</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>659</v>
+        <v>709</v>
       </c>
       <c r="S105" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T105" s="2" t="s">
-        <v>570</v>
+        <v>613</v>
       </c>
       <c r="U105" s="2" t="s">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="X105" s="2">
         <v>2</v>
@@ -7543,43 +7528,43 @@
     </row>
     <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B106" t="s">
-        <v>661</v>
+        <v>711</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>662</v>
+        <v>712</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="M106" s="4" t="s">
-        <v>663</v>
+        <v>713</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>664</v>
+        <v>714</v>
       </c>
       <c r="S106" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T106" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="U106" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="W106" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="X106" s="2">
         <v>2</v>
@@ -7587,40 +7572,40 @@
     </row>
     <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>665</v>
+        <v>715</v>
       </c>
       <c r="B107" t="s">
-        <v>666</v>
+        <v>716</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>667</v>
+        <v>717</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>668</v>
+        <v>718</v>
       </c>
       <c r="M107" s="4" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>670</v>
+        <v>720</v>
       </c>
       <c r="S107" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T107" s="2" t="s">
-        <v>671</v>
+        <v>721</v>
       </c>
       <c r="U107" s="2" t="s">
-        <v>672</v>
+        <v>365</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>673</v>
+        <v>722</v>
       </c>
       <c r="X107" s="2">
         <v>1</v>
@@ -7628,40 +7613,40 @@
     </row>
     <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>665</v>
+        <v>715</v>
       </c>
       <c r="B108" t="s">
-        <v>666</v>
+        <v>716</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>667</v>
+        <v>717</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>674</v>
+        <v>723</v>
       </c>
       <c r="M108" s="4" t="s">
-        <v>675</v>
+        <v>724</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>676</v>
+        <v>725</v>
       </c>
       <c r="S108" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T108" s="2" t="s">
-        <v>807</v>
+        <v>726</v>
       </c>
       <c r="U108" s="2" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="W108" s="1" t="s">
-        <v>673</v>
+        <v>722</v>
       </c>
       <c r="X108" s="2">
         <v>3</v>
@@ -7669,40 +7654,40 @@
     </row>
     <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>665</v>
+        <v>715</v>
       </c>
       <c r="B109" t="s">
-        <v>666</v>
+        <v>716</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>667</v>
+        <v>717</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>677</v>
+        <v>727</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>678</v>
+        <v>728</v>
       </c>
       <c r="M109" s="4" t="s">
-        <v>679</v>
+        <v>729</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>680</v>
+        <v>730</v>
       </c>
       <c r="S109" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T109" s="2" t="s">
-        <v>808</v>
+        <v>731</v>
       </c>
       <c r="U109" s="2" t="s">
-        <v>809</v>
+        <v>732</v>
       </c>
       <c r="W109" s="1" t="s">
-        <v>673</v>
+        <v>722</v>
       </c>
       <c r="X109" s="2">
         <v>3</v>
@@ -7710,43 +7695,43 @@
     </row>
     <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>665</v>
+        <v>715</v>
       </c>
       <c r="B110" t="s">
-        <v>666</v>
+        <v>716</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>667</v>
+        <v>717</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>681</v>
+        <v>733</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>682</v>
+        <v>734</v>
       </c>
       <c r="S110" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T110" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="U110" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="W110" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="U110" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="W110" s="1" t="s">
-        <v>673</v>
       </c>
       <c r="X110" s="2">
         <v>3</v>
@@ -7754,43 +7739,43 @@
     </row>
     <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>665</v>
+        <v>715</v>
       </c>
       <c r="B111" t="s">
-        <v>666</v>
+        <v>716</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>667</v>
+        <v>717</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>683</v>
+        <v>735</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="M111" s="4" t="s">
-        <v>684</v>
+        <v>736</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>685</v>
+        <v>737</v>
       </c>
       <c r="S111" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T111" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="U111" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="W111" s="1" t="s">
-        <v>673</v>
+        <v>722</v>
       </c>
       <c r="X111" s="2">
         <v>3</v>
@@ -7798,16 +7783,16 @@
     </row>
     <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>686</v>
+        <v>738</v>
       </c>
       <c r="B112" t="s">
-        <v>687</v>
+        <v>739</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>688</v>
+        <v>740</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>25</v>
@@ -7819,22 +7804,22 @@
         <v>36</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>689</v>
+        <v>741</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>690</v>
+        <v>742</v>
       </c>
       <c r="S112" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T112" s="2" t="s">
-        <v>691</v>
+        <v>549</v>
       </c>
       <c r="U112" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="W112" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X112" s="2">
         <v>1</v>
@@ -7842,43 +7827,43 @@
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>686</v>
+        <v>738</v>
       </c>
       <c r="B113" t="s">
-        <v>687</v>
+        <v>739</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>688</v>
+        <v>740</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>692</v>
+        <v>743</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>693</v>
+        <v>744</v>
       </c>
       <c r="S113" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T113" s="2" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="U113" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="W113" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X113" s="2">
         <v>3</v>
@@ -7886,19 +7871,19 @@
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>686</v>
+        <v>738</v>
       </c>
       <c r="B114" t="s">
-        <v>687</v>
+        <v>739</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>688</v>
+        <v>740</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>35</v>
@@ -7907,22 +7892,22 @@
         <v>36</v>
       </c>
       <c r="M114" s="4" t="s">
-        <v>694</v>
+        <v>745</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>695</v>
+        <v>746</v>
       </c>
       <c r="S114" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T114" s="2" t="s">
-        <v>696</v>
+        <v>747</v>
       </c>
       <c r="U114" s="2" t="s">
-        <v>697</v>
+        <v>748</v>
       </c>
       <c r="W114" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X114" s="2">
         <v>3</v>
@@ -7930,43 +7915,43 @@
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>698</v>
+        <v>749</v>
       </c>
       <c r="B115" t="s">
-        <v>699</v>
+        <v>750</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>700</v>
+        <v>751</v>
       </c>
       <c r="M115" s="4" t="s">
-        <v>701</v>
+        <v>752</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>702</v>
+        <v>753</v>
       </c>
       <c r="S115" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T115" s="2" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="U115" s="2" t="s">
-        <v>810</v>
+        <v>754</v>
       </c>
       <c r="W115" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X115" s="2">
         <v>1</v>
@@ -7974,43 +7959,43 @@
     </row>
     <row r="116" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>698</v>
+        <v>749</v>
       </c>
       <c r="B116" t="s">
-        <v>699</v>
+        <v>750</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>700</v>
+        <v>751</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>703</v>
+        <v>755</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>704</v>
+        <v>756</v>
       </c>
       <c r="S116" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T116" s="2" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="U116" s="2" t="s">
-        <v>811</v>
+        <v>757</v>
       </c>
       <c r="W116" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X116" s="2">
         <v>3</v>
@@ -8018,46 +8003,46 @@
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>705</v>
+        <v>758</v>
       </c>
       <c r="B117" t="s">
-        <v>706</v>
+        <v>759</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>707</v>
+        <v>760</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>709</v>
+        <v>762</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>710</v>
+        <v>763</v>
       </c>
       <c r="S117" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T117" s="2" t="s">
-        <v>711</v>
+        <v>764</v>
       </c>
       <c r="U117" s="2" t="s">
-        <v>562</v>
+        <v>605</v>
       </c>
       <c r="W117" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X117" s="2">
         <v>3</v>
@@ -8065,46 +8050,46 @@
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>705</v>
+        <v>758</v>
       </c>
       <c r="B118" t="s">
-        <v>706</v>
+        <v>759</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>707</v>
+        <v>760</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>712</v>
+        <v>765</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>713</v>
+        <v>766</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>714</v>
+        <v>767</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>715</v>
+        <v>768</v>
       </c>
       <c r="T118" s="2" t="s">
-        <v>716</v>
+        <v>769</v>
       </c>
       <c r="U118" s="2" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="W118" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X118" s="2">
         <v>2</v>
@@ -8112,46 +8097,46 @@
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>705</v>
+        <v>758</v>
       </c>
       <c r="B119" t="s">
-        <v>706</v>
+        <v>759</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>707</v>
+        <v>760</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H119" s="2">
         <v>1914</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>717</v>
+        <v>770</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>718</v>
+        <v>771</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>719</v>
+        <v>772</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>715</v>
+        <v>768</v>
       </c>
       <c r="T119" s="2" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="U119" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="W119" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X119" s="2">
         <v>2</v>
@@ -8159,46 +8144,46 @@
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>705</v>
+        <v>758</v>
       </c>
       <c r="B120" t="s">
-        <v>706</v>
+        <v>759</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>707</v>
+        <v>760</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H120" s="2">
         <v>1912</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M120" s="4" t="s">
-        <v>720</v>
+        <v>773</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>721</v>
+        <v>774</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>715</v>
+        <v>768</v>
       </c>
       <c r="T120" s="2" t="s">
-        <v>722</v>
+        <v>425</v>
       </c>
       <c r="U120" s="2" t="s">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="W120" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X120" s="2">
         <v>2</v>
@@ -8206,43 +8191,43 @@
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>723</v>
+        <v>775</v>
       </c>
       <c r="B121" t="s">
-        <v>724</v>
+        <v>776</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>725</v>
+        <v>777</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>726</v>
+        <v>778</v>
       </c>
       <c r="M121" s="4" t="s">
-        <v>727</v>
+        <v>779</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>728</v>
+        <v>780</v>
       </c>
       <c r="S121" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T121" s="2" t="s">
-        <v>806</v>
+        <v>684</v>
       </c>
       <c r="U121" s="2" t="s">
-        <v>622</v>
+        <v>670</v>
       </c>
       <c r="W121" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="X121" s="2">
         <v>2</v>
@@ -8250,19 +8235,19 @@
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>729</v>
+        <v>781</v>
       </c>
       <c r="B122" t="s">
-        <v>730</v>
+        <v>782</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>731</v>
+        <v>783</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>732</v>
+        <v>784</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>35</v>
@@ -8271,22 +8256,22 @@
         <v>36</v>
       </c>
       <c r="M122" s="4" t="s">
-        <v>733</v>
+        <v>785</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>734</v>
+        <v>786</v>
       </c>
       <c r="S122" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T122" s="2" t="s">
-        <v>735</v>
+        <v>148</v>
       </c>
       <c r="U122" s="2" t="s">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="W122" s="1" t="s">
-        <v>530</v>
+        <v>572</v>
       </c>
       <c r="X122" s="2">
         <v>2</v>
@@ -8294,40 +8279,40 @@
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>736</v>
+        <v>787</v>
       </c>
       <c r="B123" t="s">
-        <v>737</v>
+        <v>788</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>738</v>
+        <v>789</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>26</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>739</v>
+        <v>790</v>
       </c>
       <c r="M123" s="4" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>740</v>
+        <v>791</v>
       </c>
       <c r="S123" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T123" s="2" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="U123" s="2" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="W123" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X123" s="2">
         <v>2</v>
@@ -8335,43 +8320,43 @@
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>736</v>
+        <v>787</v>
       </c>
       <c r="B124" t="s">
-        <v>737</v>
+        <v>788</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>738</v>
+        <v>789</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>821</v>
+        <v>795</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>741</v>
+        <v>796</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>742</v>
+        <v>797</v>
       </c>
       <c r="S124" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T124" s="2" t="s">
-        <v>743</v>
+        <v>798</v>
       </c>
       <c r="U124" s="2" t="s">
-        <v>744</v>
+        <v>799</v>
       </c>
       <c r="W124" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X124" s="2">
         <v>2</v>
@@ -8379,43 +8364,43 @@
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>745</v>
+        <v>800</v>
       </c>
       <c r="B125" t="s">
-        <v>746</v>
+        <v>801</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>656</v>
+        <v>706</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="M125" s="4" t="s">
-        <v>747</v>
+        <v>802</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>748</v>
+        <v>803</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>607</v>
+        <v>653</v>
       </c>
       <c r="T125" s="2" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="U125" s="2" t="s">
-        <v>765</v>
+        <v>79</v>
       </c>
       <c r="W125" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X125" s="2">
         <v>2</v>
@@ -8423,43 +8408,43 @@
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>571</v>
+        <v>614</v>
       </c>
       <c r="B126" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="M126" s="4" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="N126" s="1" t="s">
-        <v>750</v>
+        <v>808</v>
       </c>
       <c r="S126" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T126" s="2" t="s">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="U126" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="W126" s="1" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="X126" s="2">
         <v>2</v>
@@ -8467,43 +8452,43 @@
     </row>
     <row r="127" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>751</v>
+        <v>809</v>
       </c>
       <c r="B127" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>752</v>
+        <v>811</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>753</v>
+        <v>812</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>754</v>
+        <v>813</v>
       </c>
       <c r="T127" s="2" t="s">
-        <v>755</v>
+        <v>814</v>
       </c>
       <c r="U127" s="2" t="s">
-        <v>756</v>
+        <v>815</v>
       </c>
       <c r="W127" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="X127" s="2">
         <v>1</v>
@@ -8511,43 +8496,43 @@
     </row>
     <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>751</v>
+        <v>809</v>
       </c>
       <c r="B128" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="J128" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="M128" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="N128" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="M128" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>758</v>
-      </c>
       <c r="S128" s="1" t="s">
-        <v>641</v>
+        <v>691</v>
       </c>
       <c r="T128" s="2" t="s">
-        <v>576</v>
+        <v>618</v>
       </c>
       <c r="U128" s="2" t="s">
-        <v>569</v>
+        <v>612</v>
       </c>
       <c r="W128" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="X128" s="2">
         <v>3</v>
@@ -8555,14 +8540,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C117" r:id="rId1" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C118" r:id="rId2" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C119" r:id="rId3" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="N119" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C120" r:id="rId5" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="N120" r:id="rId6" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/%28Barcelona%29_Portrait_de_famille_-_Suzanne_Valadon_%281912%29.jpg/960px-%28Barcelona%29_Portrait_de_famille_-_Suzanne_Valadon_%281912%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N47" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Paul_Klee%2C_1922%2C_Senecio%2C_oil_on_gauze%2C_40.3_%C3%97_37.4_cm%2C_Kunstmuseum_Basel.jpg/1280px-Paul_Klee%2C_1922%2C_Senecio%2C_oil_on_gauze%2C_40.3_%C3%97_37.4_cm%2C_Kunstmuseum_Basel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{E0A77EB5-3FAF-4855-969E-89E0D96761C5}"/>
-    <hyperlink ref="N46" r:id="rId8" xr:uid="{7273332B-F012-4156-A74A-734ACAD7132F}"/>
+    <hyperlink ref="N46" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N47" r:id="rId2" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Paul_Klee%2C_1922%2C_Senecio%2C_oil_on_gauze%2C_40.3_%C3%97_37.4_cm%2C_Kunstmuseum_Basel.jpg/1280px-Paul_Klee%2C_1922%2C_Senecio%2C_oil_on_gauze%2C_40.3_%C3%97_37.4_cm%2C_Kunstmuseum_Basel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C117" r:id="rId3" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C118" r:id="rId4" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C119" r:id="rId5" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N119" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C120" r:id="rId7" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N120" r:id="rId8" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/%28Barcelona%29_Portrait_de_famille_-_Suzanne_Valadon_%281912%29.jpg/960px-%28Barcelona%29_Portrait_de_famille_-_Suzanne_Valadon_%281912%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2E43A1-0F6D-4F8B-9E9C-D32E88212343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8009E87-0ABA-4BAB-AD9E-E9A4325D28F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1140" windowWidth="28800" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3364" uniqueCount="1154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3364" uniqueCount="1155">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -3482,6 +3482,9 @@
   </si>
   <si>
     <t>Le Poulet plumé</t>
+  </si>
+  <si>
+    <t>Musée de Montmartre</t>
   </si>
 </sst>
 </file>
@@ -3512,12 +3515,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3536,7 +3545,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3554,12 +3563,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF6B6B"/>
+          <bgColor rgb="FFFF6B6B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4B183"/>
+          <bgColor rgb="FFF4B183"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -17012,44 +17055,44 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="317" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
+    <row r="317" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="7" t="s">
         <v>1071</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B317" s="7" t="s">
         <v>1072</v>
       </c>
-      <c r="C317" t="s">
+      <c r="C317" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="D317" t="s">
+      <c r="D317" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E317" t="s">
-        <v>190</v>
-      </c>
-      <c r="I317" t="s">
+      <c r="E317" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I317" s="7" t="s">
         <v>1089</v>
       </c>
-      <c r="K317" s="1" t="s">
+      <c r="K317" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="R317" t="s">
-        <v>32</v>
-      </c>
-      <c r="S317">
-        <v>46</v>
-      </c>
-      <c r="T317">
-        <v>38</v>
-      </c>
-      <c r="V317">
+      <c r="R317" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S317" s="7">
+        <v>66</v>
+      </c>
+      <c r="T317" s="7">
+        <v>52</v>
+      </c>
+      <c r="V317" s="7">
         <v>2</v>
       </c>
-      <c r="W317" t="s">
+      <c r="W317" s="7" t="s">
         <v>1071</v>
       </c>
-      <c r="X317" t="s">
+      <c r="X317" s="7" t="s">
         <v>1072</v>
       </c>
     </row>
@@ -17778,20 +17821,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:X334">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>IFERROR(--$V2,0)=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>IFERROR(--$V2,0)=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>IFERROR(--$V2,0)=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>IFERROR(--$V2,0)=4</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5C1BEF-5909-4592-84A9-32D83E39DA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27801C6F-CB4C-492D-8D1B-0EE20C04AC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5786,7 +5786,7 @@
         <v>1906</v>
       </c>
       <c r="E43" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F43" t="s">
         <v>113</v>

--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32DAB43-F7DE-4CBA-9651-D5EAA99B5521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE2C26D-D8C8-4597-98E3-85EA8C64E789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1140" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="420" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -3490,7 +3490,7 @@
     <t xml:space="preserve"> Art Gallery</t>
   </si>
   <si>
-    <t>Institut of Arts</t>
+    <t>Institute of Arts</t>
   </si>
 </sst>
 </file>

--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1913-1515</t>
+          <t>1913-1915</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">

--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -9360,8 +9360,10 @@
       <c r="R145" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="S145" s="2" t="s">
-        <v>205</v>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquarelle sur papier</t>
+        </is>
       </c>
       <c r="T145" s="2">
         <v>23</v>
@@ -14614,8 +14616,10 @@
       <c r="R279" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="S279" s="2" t="s">
-        <v>964</v>
+      <c r="S279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gouache, aquarelle et crayon sur papier</t>
+        </is>
       </c>
       <c r="T279" s="2">
         <v>46</v>

--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -3824,7 +3824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W329"/>
+  <dimension ref="A1:X329"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="2" customWidth="1"/>
@@ -3834,6 +3834,7 @@
     <col min="12" max="21" width="9.140625" style="2" customWidth="1"/>
     <col min="22" max="22" width="4.7109375" style="2" customWidth="1"/>
     <col min="23" max="23" width="10.5703125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3905,6 +3906,11 @@
       </c>
       <c r="W1" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
